--- a/Resource/HotelBooking.xlsx
+++ b/Resource/HotelBooking.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2480119\IdeaProjects\HotelProjectPomTekstack\Resource\"/>
     </mc:Choice>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="29">
   <si>
     <t>Browser</t>
   </si>
@@ -125,7 +125,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -133,18 +133,8 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor indexed="17"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none">
-        <fgColor indexed="10"/>
       </patternFill>
     </fill>
     <fill>
@@ -165,21 +155,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,60 +500,60 @@
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" customWidth="true" width="15.81640625"/>
-    <col min="4" max="4" customWidth="true" width="14.81640625"/>
-    <col min="5" max="5" customWidth="true" width="15.26953125"/>
-    <col min="7" max="7" customWidth="true" width="14.0"/>
-    <col min="9" max="9" customWidth="true" width="16.90625"/>
-    <col min="12" max="12" customWidth="true" width="18.08984375"/>
+    <col min="2" max="2" width="15.81640625" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="9" max="9" width="16.90625" customWidth="1"/>
+    <col min="12" max="12" width="18.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -597,24 +580,24 @@
       <c r="J2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>15</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>15</v>
       </c>
-      <c r="M2" t="s" s="11">
+      <c r="M2" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="0">
+      <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s" s="0">
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s" s="0">
+      <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -638,24 +621,24 @@
       <c r="J3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K3" t="s" s="0">
+      <c r="K3" t="s">
         <v>15</v>
       </c>
-      <c r="L3" t="s" s="0">
+      <c r="L3" t="s">
         <v>27</v>
       </c>
-      <c r="M3" t="s" s="12">
+      <c r="M3" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="0">
+      <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s" s="0">
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s" s="0">
+      <c r="C4" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -679,13 +662,13 @@
       <c r="J4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="K4" t="s" s="0">
+      <c r="K4" t="s">
         <v>15</v>
       </c>
-      <c r="L4" t="s" s="0">
+      <c r="L4" t="s">
         <v>27</v>
       </c>
-      <c r="M4" t="s" s="13">
+      <c r="M4" s="6" t="s">
         <v>28</v>
       </c>
     </row>
